--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/113.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/113.xlsx
@@ -426,13 +426,13 @@
         <v>-22.08449143352865</v>
       </c>
       <c r="E2">
-        <v>-14.51170987256562</v>
+        <v>-17.05432123060032</v>
       </c>
       <c r="F2">
-        <v>-3.456771520558025</v>
+        <v>-4.795017283863488</v>
       </c>
       <c r="G2">
-        <v>-11.54585977343053</v>
+        <v>-11.40066586716917</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-22.17918283687773</v>
       </c>
       <c r="E3">
-        <v>-16.28649129175576</v>
+        <v>-17.0641117914049</v>
       </c>
       <c r="F3">
-        <v>-3.266755635499458</v>
+        <v>-4.793176651494467</v>
       </c>
       <c r="G3">
-        <v>-9.444027516002642</v>
+        <v>-11.78306036131931</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-22.20203693514392</v>
       </c>
       <c r="E4">
-        <v>-14.50204610903325</v>
+        <v>-16.92415477372384</v>
       </c>
       <c r="F4">
-        <v>-3.604611907670459</v>
+        <v>-4.531951819389046</v>
       </c>
       <c r="G4">
-        <v>-10.51154272005049</v>
+        <v>-11.18844665591973</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-22.09644671257774</v>
       </c>
       <c r="E5">
-        <v>-15.88198987949461</v>
+        <v>-18.01171309140595</v>
       </c>
       <c r="F5">
-        <v>-3.78708964936355</v>
+        <v>-4.732682636802825</v>
       </c>
       <c r="G5">
-        <v>-9.673676749516344</v>
+        <v>-11.37524749851865</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-21.87018941048244</v>
       </c>
       <c r="E6">
-        <v>-17.95657439188856</v>
+        <v>-19.09226133132419</v>
       </c>
       <c r="F6">
-        <v>-3.702346007322356</v>
+        <v>-4.397495364403644</v>
       </c>
       <c r="G6">
-        <v>-10.84155776267828</v>
+        <v>-11.67510016073813</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-21.51205849671182</v>
       </c>
       <c r="E7">
-        <v>-17.08102111334954</v>
+        <v>-18.96418250096525</v>
       </c>
       <c r="F7">
-        <v>-3.717450458545001</v>
+        <v>-4.720396291484503</v>
       </c>
       <c r="G7">
-        <v>-10.26013327070716</v>
+        <v>-12.07348127929741</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-21.01105641036321</v>
       </c>
       <c r="E8">
-        <v>-17.68805399712974</v>
+        <v>-19.52705370622265</v>
       </c>
       <c r="F8">
-        <v>-3.941419466709515</v>
+        <v>-4.179913897282118</v>
       </c>
       <c r="G8">
-        <v>-11.0474869374031</v>
+        <v>-11.94448256181417</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-20.35261857575068</v>
       </c>
       <c r="E9">
-        <v>-19.99292952670975</v>
+        <v>-20.0153952862618</v>
       </c>
       <c r="F9">
-        <v>-3.236892162261133</v>
+        <v>-4.159922906750357</v>
       </c>
       <c r="G9">
-        <v>-9.117604415284964</v>
+        <v>-10.54716087950751</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-19.56379153196484</v>
       </c>
       <c r="E10">
-        <v>-20.29970646988537</v>
+        <v>-20.30996346351274</v>
       </c>
       <c r="F10">
-        <v>-3.279498411256723</v>
+        <v>-4.338581046349141</v>
       </c>
       <c r="G10">
-        <v>-9.701796523326914</v>
+        <v>-11.59869276969176</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-18.65902857821996</v>
       </c>
       <c r="E11">
-        <v>-20.36879286934639</v>
+        <v>-21.6749134565347</v>
       </c>
       <c r="F11">
-        <v>-3.056063700067015</v>
+        <v>-4.089700545280238</v>
       </c>
       <c r="G11">
-        <v>-9.178356236476128</v>
+        <v>-11.52778088424057</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-17.65380668709647</v>
       </c>
       <c r="E12">
-        <v>-19.54624085059314</v>
+        <v>-21.30122830989575</v>
       </c>
       <c r="F12">
-        <v>-3.615871077409309</v>
+        <v>-4.441264641232765</v>
       </c>
       <c r="G12">
-        <v>-9.171082967926351</v>
+        <v>-10.7192827631853</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-16.56462803412006</v>
       </c>
       <c r="E13">
-        <v>-20.91269882545966</v>
+        <v>-21.97906841325988</v>
       </c>
       <c r="F13">
-        <v>-3.433998043920261</v>
+        <v>-4.183411264456738</v>
       </c>
       <c r="G13">
-        <v>-8.960694488360128</v>
+        <v>-10.38153759672331</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.4473106014356</v>
       </c>
       <c r="E14">
-        <v>-22.16126250801048</v>
+        <v>-21.90529957167493</v>
       </c>
       <c r="F14">
-        <v>-3.030739680196031</v>
+        <v>-3.83689523945687</v>
       </c>
       <c r="G14">
-        <v>-8.032205644233972</v>
+        <v>-9.783418023597646</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-14.34141534580011</v>
       </c>
       <c r="E15">
-        <v>-21.98885444559046</v>
+        <v>-23.38362443995293</v>
       </c>
       <c r="F15">
-        <v>-2.455183381791712</v>
+        <v>-3.855456467851399</v>
       </c>
       <c r="G15">
-        <v>-9.437482567471502</v>
+        <v>-8.715889577367641</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-13.28024321973163</v>
       </c>
       <c r="E16">
-        <v>-22.96757994744623</v>
+        <v>-23.73115764919758</v>
       </c>
       <c r="F16">
-        <v>-2.688539449364749</v>
+        <v>-3.701115881729198</v>
       </c>
       <c r="G16">
-        <v>-8.506146654181576</v>
+        <v>-8.719157085814901</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-12.29613745687592</v>
       </c>
       <c r="E17">
-        <v>-23.54091192766134</v>
+        <v>-25.77906039273833</v>
       </c>
       <c r="F17">
-        <v>-1.837450757073856</v>
+        <v>-3.433698174920448</v>
       </c>
       <c r="G17">
-        <v>-7.106580421999288</v>
+        <v>-8.700214144239192</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-11.4375784578958</v>
       </c>
       <c r="E18">
-        <v>-25.13137539779128</v>
+        <v>-25.77818639725485</v>
       </c>
       <c r="F18">
-        <v>-2.132269200832409</v>
+        <v>-3.445373185095504</v>
       </c>
       <c r="G18">
-        <v>-7.186917430600782</v>
+        <v>-9.307858156881339</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.72468252593931</v>
       </c>
       <c r="E19">
-        <v>-26.87179475621121</v>
+        <v>-26.31360146460374</v>
       </c>
       <c r="F19">
-        <v>-2.047493252462504</v>
+        <v>-3.260397087315569</v>
       </c>
       <c r="G19">
-        <v>-7.153057170825116</v>
+        <v>-9.206019155002279</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-10.15652687725038</v>
       </c>
       <c r="E20">
-        <v>-24.98967491761726</v>
+        <v>-26.67447555827499</v>
       </c>
       <c r="F20">
-        <v>-2.204504495091331</v>
+        <v>-2.62823264570614</v>
       </c>
       <c r="G20">
-        <v>-7.478980379166365</v>
+        <v>-9.004046082196883</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.730341760377033</v>
       </c>
       <c r="E21">
-        <v>-28.09753040128937</v>
+        <v>-27.56744534784751</v>
       </c>
       <c r="F21">
-        <v>-1.437846321963375</v>
+        <v>-2.65664481925476</v>
       </c>
       <c r="G21">
-        <v>-7.814716044486013</v>
+        <v>-8.447252049037941</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.447400008087818</v>
       </c>
       <c r="E22">
-        <v>-25.98848873017106</v>
+        <v>-28.40223330336948</v>
       </c>
       <c r="F22">
-        <v>-1.585312287009743</v>
+        <v>-2.328358675688302</v>
       </c>
       <c r="G22">
-        <v>-6.966107353676933</v>
+        <v>-8.689113885046016</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.289926717601448</v>
       </c>
       <c r="E23">
-        <v>-27.68361429156628</v>
+        <v>-29.61444013234972</v>
       </c>
       <c r="F23">
-        <v>-1.559191377697266</v>
+        <v>-2.284464315381359</v>
       </c>
       <c r="G23">
-        <v>-6.175803990905497</v>
+        <v>-8.783917977654124</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.226569073224757</v>
       </c>
       <c r="E24">
-        <v>-28.44466963329536</v>
+        <v>-28.83668151424335</v>
       </c>
       <c r="F24">
-        <v>-1.324849552914897</v>
+        <v>-2.409904819554691</v>
       </c>
       <c r="G24">
-        <v>-7.496373985429695</v>
+        <v>-8.061560251530691</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.238589046518998</v>
       </c>
       <c r="E25">
-        <v>-28.71523689830564</v>
+        <v>-29.33112747724484</v>
       </c>
       <c r="F25">
-        <v>-1.545583786371479</v>
+        <v>-1.865782578984405</v>
       </c>
       <c r="G25">
-        <v>-6.887680529851599</v>
+        <v>-9.415715730550795</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.308470179298036</v>
       </c>
       <c r="E26">
-        <v>-28.96927070471393</v>
+        <v>-30.57378376545266</v>
       </c>
       <c r="F26">
-        <v>-1.061301978612026</v>
+        <v>-1.996022643889557</v>
       </c>
       <c r="G26">
-        <v>-6.87377623858666</v>
+        <v>-8.558310920243871</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.409467061504506</v>
       </c>
       <c r="E27">
-        <v>-29.10819523032124</v>
+        <v>-30.59336715129884</v>
       </c>
       <c r="F27">
-        <v>-0.9413626623606856</v>
+        <v>-1.990719435776835</v>
       </c>
       <c r="G27">
-        <v>-8.063351256667437</v>
+        <v>-8.040425728807984</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.508136890223717</v>
       </c>
       <c r="E28">
-        <v>-28.39376505697513</v>
+        <v>-30.08759094633015</v>
       </c>
       <c r="F28">
-        <v>-0.2168650765656127</v>
+        <v>-2.212590189310057</v>
       </c>
       <c r="G28">
-        <v>-6.084813646758629</v>
+        <v>-8.940715346030625</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.594683775709402</v>
       </c>
       <c r="E29">
-        <v>-29.53085582335315</v>
+        <v>-29.47429971147135</v>
       </c>
       <c r="F29">
-        <v>-0.7721992699327901</v>
+        <v>-2.129569551466685</v>
       </c>
       <c r="G29">
-        <v>-7.500091728070298</v>
+        <v>-8.518044754849717</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.662846948472573</v>
       </c>
       <c r="E30">
-        <v>-28.31544509901248</v>
+        <v>-30.27477994791121</v>
       </c>
       <c r="F30">
-        <v>-0.7720857835986066</v>
+        <v>-1.959373184887499</v>
       </c>
       <c r="G30">
-        <v>-6.829064010533263</v>
+        <v>-8.81455707662008</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.705965414361284</v>
       </c>
       <c r="E31">
-        <v>-29.45471858986219</v>
+        <v>-31.03259063801379</v>
       </c>
       <c r="F31">
-        <v>-1.468372489123939</v>
+        <v>-1.769866745781653</v>
       </c>
       <c r="G31">
-        <v>-7.275299064862705</v>
+        <v>-9.260103537477352</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.714865397224704</v>
       </c>
       <c r="E32">
-        <v>-29.2186899961084</v>
+        <v>-30.91879235043804</v>
       </c>
       <c r="F32">
-        <v>-0.7348945723151171</v>
+        <v>-1.830909968061351</v>
       </c>
       <c r="G32">
-        <v>-5.847963976697011</v>
+        <v>-8.422307088399533</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.702555353277692</v>
       </c>
       <c r="E33">
-        <v>-30.21422292924364</v>
+        <v>-30.21128168537566</v>
       </c>
       <c r="F33">
-        <v>-1.06217010765016</v>
+        <v>-1.655723516247701</v>
       </c>
       <c r="G33">
-        <v>-7.19387950786987</v>
+        <v>-8.3667594447961</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.680433883749561</v>
       </c>
       <c r="E34">
-        <v>-28.93066093532453</v>
+        <v>-28.85238626210195</v>
       </c>
       <c r="F34">
-        <v>-0.9701434594035515</v>
+        <v>-1.654040273685212</v>
       </c>
       <c r="G34">
-        <v>-6.984715930153176</v>
+        <v>-7.662973879147979</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.655320849714885</v>
       </c>
       <c r="E35">
-        <v>-29.86838110504085</v>
+        <v>-29.84113101269969</v>
       </c>
       <c r="F35">
-        <v>-0.9042841090439768</v>
+        <v>-1.615496338432951</v>
       </c>
       <c r="G35">
-        <v>-7.580918697411604</v>
+        <v>-8.489411846480559</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.626714309170985</v>
       </c>
       <c r="E36">
-        <v>-26.96921581753822</v>
+        <v>-29.9341798323723</v>
       </c>
       <c r="F36">
-        <v>-1.394123433708811</v>
+        <v>-1.792043797889401</v>
       </c>
       <c r="G36">
-        <v>-7.751613735961965</v>
+        <v>-8.2671087135185</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.609985948583304</v>
       </c>
       <c r="E37">
-        <v>-28.27963845503383</v>
+        <v>-28.90420106169771</v>
       </c>
       <c r="F37">
-        <v>-1.318065223885969</v>
+        <v>-2.104220680573618</v>
       </c>
       <c r="G37">
-        <v>-8.786232048986076</v>
+        <v>-9.197507742420813</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.612053136800986</v>
       </c>
       <c r="E38">
-        <v>-26.1219383307031</v>
+        <v>-29.41292530324539</v>
       </c>
       <c r="F38">
-        <v>-0.7874462003487178</v>
+        <v>-2.347611590864168</v>
       </c>
       <c r="G38">
-        <v>-8.249350947245849</v>
+        <v>-8.587721806814757</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.631368309487096</v>
       </c>
       <c r="E39">
-        <v>-26.41301505449413</v>
+        <v>-28.03013765110722</v>
       </c>
       <c r="F39">
-        <v>-0.7082435078648487</v>
+        <v>-1.967382669305167</v>
       </c>
       <c r="G39">
-        <v>-7.362631256188679</v>
+        <v>-8.046166214773079</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.658757108125533</v>
       </c>
       <c r="E40">
-        <v>-28.05714999856297</v>
+        <v>-27.44911179355308</v>
       </c>
       <c r="F40">
-        <v>-1.334386546823328</v>
+        <v>-1.872030125936319</v>
       </c>
       <c r="G40">
-        <v>-6.848811414675016</v>
+        <v>-8.786870984275154</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.700773268888836</v>
       </c>
       <c r="E41">
-        <v>-26.97815502522937</v>
+        <v>-27.13835885019872</v>
       </c>
       <c r="F41">
-        <v>-1.514549001625595</v>
+        <v>-1.821348951498239</v>
       </c>
       <c r="G41">
-        <v>-5.949068037466353</v>
+        <v>-8.156212059043993</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.754564977114184</v>
       </c>
       <c r="E42">
-        <v>-27.29362211002571</v>
+        <v>-27.37561013193458</v>
       </c>
       <c r="F42">
-        <v>-0.9637492914213421</v>
+        <v>-2.094793031162356</v>
       </c>
       <c r="G42">
-        <v>-7.898211313531972</v>
+        <v>-9.160800413481374</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.810895649545136</v>
       </c>
       <c r="E43">
-        <v>-24.02604281962906</v>
+        <v>-27.8539528413648</v>
       </c>
       <c r="F43">
-        <v>-0.6193621706466701</v>
+        <v>-1.651109509814108</v>
       </c>
       <c r="G43">
-        <v>-7.088984872458062</v>
+        <v>-8.071207181232127</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.857785530284188</v>
       </c>
       <c r="E44">
-        <v>-24.11111473233715</v>
+        <v>-25.93930950244776</v>
       </c>
       <c r="F44">
-        <v>-1.107137203743728</v>
+        <v>-1.94570015253689</v>
       </c>
       <c r="G44">
-        <v>-6.250456792816063</v>
+        <v>-8.223426065127816</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.900781930042141</v>
       </c>
       <c r="E45">
-        <v>-25.46058187272689</v>
+        <v>-25.59464281724996</v>
       </c>
       <c r="F45">
-        <v>-1.112939917400339</v>
+        <v>-1.725679143414119</v>
       </c>
       <c r="G45">
-        <v>-6.652777460567073</v>
+        <v>-7.438767182500838</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.936391403747454</v>
       </c>
       <c r="E46">
-        <v>-24.68136282175304</v>
+        <v>-23.94592958595936</v>
       </c>
       <c r="F46">
-        <v>-0.4356236537665173</v>
+        <v>-1.913359032396792</v>
       </c>
       <c r="G46">
-        <v>-7.386162613881819</v>
+        <v>-7.654310181471706</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.955929909469132</v>
       </c>
       <c r="E47">
-        <v>-22.81594852377339</v>
+        <v>-24.1263168195809</v>
       </c>
       <c r="F47">
-        <v>-1.084144209744222</v>
+        <v>-1.79643166002203</v>
       </c>
       <c r="G47">
-        <v>-6.534753201546516</v>
+        <v>-8.368070420829653</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.951617106458713</v>
       </c>
       <c r="E48">
-        <v>-22.63447445639001</v>
+        <v>-23.64622611918372</v>
       </c>
       <c r="F48">
-        <v>-1.170578549654531</v>
+        <v>-2.133836471958505</v>
       </c>
       <c r="G48">
-        <v>-6.737815443834331</v>
+        <v>-8.60701235567209</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.931092287811643</v>
       </c>
       <c r="E49">
-        <v>-21.79911138466907</v>
+        <v>-23.62124252808341</v>
       </c>
       <c r="F49">
-        <v>-1.112288820621738</v>
+        <v>-2.041152099994074</v>
       </c>
       <c r="G49">
-        <v>-8.052207960382249</v>
+        <v>-8.15985696968273</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.892877459975887</v>
       </c>
       <c r="E50">
-        <v>-21.41725234244628</v>
+        <v>-22.91339222747045</v>
       </c>
       <c r="F50">
-        <v>-0.9896672507201331</v>
+        <v>-1.787765280253942</v>
       </c>
       <c r="G50">
-        <v>-7.628818980819318</v>
+        <v>-8.516806610818028</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.829711080093521</v>
       </c>
       <c r="E51">
-        <v>-22.56552843962323</v>
+        <v>-22.95763994699939</v>
       </c>
       <c r="F51">
-        <v>-1.067623250262789</v>
+        <v>-2.120163439607897</v>
       </c>
       <c r="G51">
-        <v>-6.944542460034121</v>
+        <v>-7.081410344264209</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.739576841032441</v>
       </c>
       <c r="E52">
-        <v>-20.01485639785489</v>
+        <v>-21.75631277682258</v>
       </c>
       <c r="F52">
-        <v>-1.175122973226289</v>
+        <v>-2.092218465274455</v>
       </c>
       <c r="G52">
-        <v>-8.092871391241118</v>
+        <v>-8.250228241813755</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.631031833886764</v>
       </c>
       <c r="E53">
-        <v>-21.89299117932208</v>
+        <v>-20.75119079997609</v>
       </c>
       <c r="F53">
-        <v>-1.282214311060209</v>
+        <v>-1.950427645304667</v>
       </c>
       <c r="G53">
-        <v>-7.38743055282336</v>
+        <v>-8.675537337789464</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.504753649802659</v>
       </c>
       <c r="E54">
-        <v>-19.82705152380878</v>
+        <v>-22.070059041496</v>
       </c>
       <c r="F54">
-        <v>-1.433947196598398</v>
+        <v>-2.120216455121676</v>
       </c>
       <c r="G54">
-        <v>-8.351166775306133</v>
+        <v>-9.514932780362752</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.354963592388502</v>
       </c>
       <c r="E55">
-        <v>-19.35642986256164</v>
+        <v>-20.66265007617812</v>
       </c>
       <c r="F55">
-        <v>-0.720447016442891</v>
+        <v>-2.294805654037908</v>
       </c>
       <c r="G55">
-        <v>-9.016407659240523</v>
+        <v>-9.028120369358463</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.185077757488568</v>
       </c>
       <c r="E56">
-        <v>-18.92858416679095</v>
+        <v>-20.30015931728613</v>
       </c>
       <c r="F56">
-        <v>-1.596140705699138</v>
+        <v>-2.118759356860151</v>
       </c>
       <c r="G56">
-        <v>-6.028785974052004</v>
+        <v>-8.188506430779583</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.004907076417533</v>
       </c>
       <c r="E57">
-        <v>-17.8306737575273</v>
+        <v>-20.20021589593685</v>
       </c>
       <c r="F57">
-        <v>-0.6141658219289088</v>
+        <v>-1.978544091690488</v>
       </c>
       <c r="G57">
-        <v>-6.974992857904337</v>
+        <v>-9.135650199019532</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.817909366837698</v>
       </c>
       <c r="E58">
-        <v>-18.41919876803815</v>
+        <v>-18.16875151304394</v>
       </c>
       <c r="F58">
-        <v>-0.5897770288556857</v>
+        <v>-1.997737364413352</v>
       </c>
       <c r="G58">
-        <v>-7.022840172583424</v>
+        <v>-8.972218497382331</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.620047432705078</v>
       </c>
       <c r="E59">
-        <v>-17.5688373904038</v>
+        <v>-19.31527961925394</v>
       </c>
       <c r="F59">
-        <v>-1.231188535782565</v>
+        <v>-1.911365980425656</v>
       </c>
       <c r="G59">
-        <v>-7.768196258568175</v>
+        <v>-8.983196266390554</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.419319722120287</v>
       </c>
       <c r="E60">
-        <v>-16.97202980093293</v>
+        <v>-18.49112452070198</v>
       </c>
       <c r="F60">
-        <v>-0.7171691666300133</v>
+        <v>-2.251709011539861</v>
       </c>
       <c r="G60">
-        <v>-7.58388494621479</v>
+        <v>-9.07883130592902</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.224170939191369</v>
       </c>
       <c r="E61">
-        <v>-17.80406444425823</v>
+        <v>-17.71649734237191</v>
       </c>
       <c r="F61">
-        <v>-1.050297946033237</v>
+        <v>-2.358715027531293</v>
       </c>
       <c r="G61">
-        <v>-7.270876176022239</v>
+        <v>-8.87324311739474</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.036240224088628</v>
       </c>
       <c r="E62">
-        <v>-16.1022548552277</v>
+        <v>-18.30462384717008</v>
       </c>
       <c r="F62">
-        <v>-0.7949619777943177</v>
+        <v>-2.065924427174794</v>
       </c>
       <c r="G62">
-        <v>-7.810266671281233</v>
+        <v>-8.2400317615528</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.848892504777028</v>
       </c>
       <c r="E63">
-        <v>-15.80055433141468</v>
+        <v>-17.85227457854389</v>
       </c>
       <c r="F63">
-        <v>-2.051200196590032</v>
+        <v>-2.451690156454107</v>
       </c>
       <c r="G63">
-        <v>-7.80791618394835</v>
+        <v>-9.363157509569325</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.668343278946421</v>
       </c>
       <c r="E64">
-        <v>-16.75377546765925</v>
+        <v>-17.91862577970428</v>
       </c>
       <c r="F64">
-        <v>-2.162342251023642</v>
+        <v>-1.868153366491217</v>
       </c>
       <c r="G64">
-        <v>-8.14382730818158</v>
+        <v>-8.704441710892841</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.498498257477256</v>
       </c>
       <c r="E65">
-        <v>-17.2121249643456</v>
+        <v>-17.67461801474898</v>
       </c>
       <c r="F65">
-        <v>-0.9375364333271546</v>
+        <v>-2.718952130191131</v>
       </c>
       <c r="G65">
-        <v>-7.501058407367765</v>
+        <v>-9.390035828802668</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.338308299915838</v>
       </c>
       <c r="E66">
-        <v>-17.34847278824255</v>
+        <v>-16.87519744122691</v>
       </c>
       <c r="F66">
-        <v>-1.285761380278997</v>
+        <v>-2.229140970017991</v>
       </c>
       <c r="G66">
-        <v>-8.199437852150258</v>
+        <v>-8.729535646080517</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.181222935038631</v>
       </c>
       <c r="E67">
-        <v>-15.45771262124197</v>
+        <v>-16.81940664145241</v>
       </c>
       <c r="F67">
-        <v>-1.113711955819748</v>
+        <v>-2.388416140758669</v>
       </c>
       <c r="G67">
-        <v>-7.544515938661777</v>
+        <v>-9.661503873568444</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.03530912379204</v>
       </c>
       <c r="E68">
-        <v>-16.54130852416737</v>
+        <v>-16.11173295132575</v>
       </c>
       <c r="F68">
-        <v>-2.120183320425564</v>
+        <v>-2.388152719924579</v>
       </c>
       <c r="G68">
-        <v>-7.831728938012327</v>
+        <v>-8.448735173439534</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.90515236838495</v>
       </c>
       <c r="E69">
-        <v>-17.55830868833597</v>
+        <v>-16.91880664592078</v>
       </c>
       <c r="F69">
-        <v>-1.288930713962108</v>
+        <v>-2.363800375017079</v>
       </c>
       <c r="G69">
-        <v>-6.875514274994777</v>
+        <v>-9.327231469377155</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.790687248896619</v>
       </c>
       <c r="E70">
-        <v>-15.60160035436169</v>
+        <v>-16.40617885977849</v>
       </c>
       <c r="F70">
-        <v>-1.479494978241328</v>
+        <v>-2.632779554380106</v>
       </c>
       <c r="G70">
-        <v>-8.659107100278062</v>
+        <v>-9.153934342032926</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.686991081280208</v>
       </c>
       <c r="E71">
-        <v>-13.75943071346341</v>
+        <v>-17.34688782233987</v>
       </c>
       <c r="F71">
-        <v>-1.57453191362971</v>
+        <v>-2.518296694211006</v>
       </c>
       <c r="G71">
-        <v>-7.854780266602273</v>
+        <v>-9.175605173132995</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.60249838142999</v>
       </c>
       <c r="E72">
-        <v>-13.57135865945085</v>
+        <v>-16.49193004358773</v>
       </c>
       <c r="F72">
-        <v>-1.735901197164665</v>
+        <v>-2.217933159058114</v>
       </c>
       <c r="G72">
-        <v>-7.853760618576177</v>
+        <v>-9.225392467498095</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.539591729285371</v>
       </c>
       <c r="E73">
-        <v>-15.54128108057952</v>
+        <v>-17.00509218966293</v>
       </c>
       <c r="F73">
-        <v>-1.444834429373391</v>
+        <v>-2.931029095921054</v>
       </c>
       <c r="G73">
-        <v>-7.51061926288518</v>
+        <v>-9.058342339586471</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.495528717913843</v>
       </c>
       <c r="E74">
-        <v>-16.6071525362389</v>
+        <v>-16.1430518775628</v>
       </c>
       <c r="F74">
-        <v>-2.341925677011353</v>
+        <v>-3.114182785414831</v>
       </c>
       <c r="G74">
-        <v>-7.547747031108106</v>
+        <v>-8.176181269736876</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.463458161656852</v>
       </c>
       <c r="E75">
-        <v>-17.34345071056804</v>
+        <v>-15.59866137473071</v>
       </c>
       <c r="F75">
-        <v>-1.812683400097554</v>
+        <v>-2.825542305746357</v>
       </c>
       <c r="G75">
-        <v>-7.191343629986788</v>
+        <v>-8.454409448493845</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.449100968004609</v>
       </c>
       <c r="E76">
-        <v>-15.23131156322849</v>
+        <v>-18.02356863635803</v>
       </c>
       <c r="F76">
-        <v>-1.677788738756071</v>
+        <v>-2.933663304261957</v>
       </c>
       <c r="G76">
-        <v>-7.103587688831787</v>
+        <v>-8.745227631936661</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.45123951113785</v>
       </c>
       <c r="E77">
-        <v>-16.40371536991831</v>
+        <v>-17.27583606515952</v>
       </c>
       <c r="F77">
-        <v>-2.090657821087581</v>
+        <v>-3.230314925082905</v>
       </c>
       <c r="G77">
-        <v>-5.698863626699316</v>
+        <v>-8.487150743877237</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.464261444323253</v>
       </c>
       <c r="E78">
-        <v>-15.57164902727495</v>
+        <v>-17.75171075625556</v>
       </c>
       <c r="F78">
-        <v>-2.411947573569995</v>
+        <v>-3.196353518302931</v>
       </c>
       <c r="G78">
-        <v>-7.565289611920704</v>
+        <v>-8.618397321781643</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.481175398356711</v>
       </c>
       <c r="E79">
-        <v>-15.44904512199129</v>
+        <v>-17.77576148171029</v>
       </c>
       <c r="F79">
-        <v>-1.992855795308655</v>
+        <v>-3.447202220320885</v>
       </c>
       <c r="G79">
-        <v>-7.162985496897391</v>
+        <v>-8.55123628442645</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.508034814693699</v>
       </c>
       <c r="E80">
-        <v>-17.0459888384262</v>
+        <v>-17.97860088946187</v>
       </c>
       <c r="F80">
-        <v>-2.380471268998419</v>
+        <v>-3.399296905049587</v>
       </c>
       <c r="G80">
-        <v>-6.547561702237956</v>
+        <v>-8.160909723164218</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.544464425581489</v>
       </c>
       <c r="E81">
-        <v>-17.54843208652524</v>
+        <v>-18.95192845030049</v>
       </c>
       <c r="F81">
-        <v>-2.884274382972245</v>
+        <v>-3.470013801859178</v>
       </c>
       <c r="G81">
-        <v>-7.148654145257886</v>
+        <v>-7.93315081115344</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.586135376382098</v>
       </c>
       <c r="E82">
-        <v>-18.27107238324725</v>
+        <v>-19.91748514974196</v>
       </c>
       <c r="F82">
-        <v>-2.562532341887903</v>
+        <v>-3.708248125067302</v>
       </c>
       <c r="G82">
-        <v>-6.72592065371173</v>
+        <v>-8.950607256101968</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.631413988494881</v>
       </c>
       <c r="E83">
-        <v>-19.87417935280661</v>
+        <v>-20.92606235225629</v>
       </c>
       <c r="F83">
-        <v>-3.158488015953562</v>
+        <v>-3.595653942576585</v>
       </c>
       <c r="G83">
-        <v>-6.00427469487924</v>
+        <v>-8.242147200152395</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.68917743103</v>
       </c>
       <c r="E84">
-        <v>-20.8376257833605</v>
+        <v>-21.83899365525462</v>
       </c>
       <c r="F84">
-        <v>-3.355353671065879</v>
+        <v>-3.618125065112327</v>
       </c>
       <c r="G84">
-        <v>-6.09067331236314</v>
+        <v>-7.918299703864269</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.7623216011886</v>
       </c>
       <c r="E85">
-        <v>-20.03487225296879</v>
+        <v>-22.07797481406141</v>
       </c>
       <c r="F85">
-        <v>-2.253405507980795</v>
+        <v>-3.804974101589992</v>
       </c>
       <c r="G85">
-        <v>-6.429540753762938</v>
+        <v>-8.490858554881221</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.847617042684604</v>
       </c>
       <c r="E86">
-        <v>-22.03632643861286</v>
+        <v>-23.3011880991173</v>
       </c>
       <c r="F86">
-        <v>-2.967649562064015</v>
+        <v>-3.959302262201151</v>
       </c>
       <c r="G86">
-        <v>-6.425879290396504</v>
+        <v>-7.958781054718477</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.947921284654475</v>
       </c>
       <c r="E87">
-        <v>-22.18798050465574</v>
+        <v>-23.71674351643117</v>
       </c>
       <c r="F87">
-        <v>-3.511801623860802</v>
+        <v>-3.933183009623479</v>
       </c>
       <c r="G87">
-        <v>-7.036204844925462</v>
+        <v>-7.807475881391627</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.072000185031261</v>
       </c>
       <c r="E88">
-        <v>-22.91812901128247</v>
+        <v>-24.29146120969263</v>
       </c>
       <c r="F88">
-        <v>-3.701123337035823</v>
+        <v>-4.398854715311638</v>
       </c>
       <c r="G88">
-        <v>-5.123461017064129</v>
+        <v>-8.772725023185849</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.222206073409405</v>
       </c>
       <c r="E89">
-        <v>-25.51036791596722</v>
+        <v>-26.51212070815199</v>
       </c>
       <c r="F89">
-        <v>-3.616484069287381</v>
+        <v>-4.19185978359789</v>
       </c>
       <c r="G89">
-        <v>-6.797120556624836</v>
+        <v>-8.066486343293127</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.391559226722214</v>
       </c>
       <c r="E90">
-        <v>-26.81836329139471</v>
+        <v>-27.11605611571094</v>
       </c>
       <c r="F90">
-        <v>-4.15383109287017</v>
+        <v>-4.613404357738919</v>
       </c>
       <c r="G90">
-        <v>-8.665496453168855</v>
+        <v>-8.82786546968795</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.582516122703888</v>
       </c>
       <c r="E91">
-        <v>-30.23709851569338</v>
+        <v>-28.29569642386502</v>
       </c>
       <c r="F91">
-        <v>-4.17138088466588</v>
+        <v>-4.432189047967693</v>
       </c>
       <c r="G91">
-        <v>-7.248940501279028</v>
+        <v>-9.371821207245597</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.798422288545398</v>
       </c>
       <c r="E92">
-        <v>-30.10458857351794</v>
+        <v>-30.70981233193207</v>
       </c>
       <c r="F92">
-        <v>-4.028065040307538</v>
+        <v>-4.635176338186699</v>
       </c>
       <c r="G92">
-        <v>-9.122785419053923</v>
+        <v>-9.693367874383929</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.03646380526421</v>
       </c>
       <c r="E93">
-        <v>-31.3014529325602</v>
+        <v>-32.02360641832638</v>
       </c>
       <c r="F93">
-        <v>-4.192460349964919</v>
+        <v>-4.547353654509298</v>
       </c>
       <c r="G93">
-        <v>-8.850205030986951</v>
+        <v>-9.479082882717984</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.282465634253457</v>
       </c>
       <c r="E94">
-        <v>-34.23599692324774</v>
+        <v>-33.7513845415539</v>
       </c>
       <c r="F94">
-        <v>-4.412379469897146</v>
+        <v>-4.921462597696416</v>
       </c>
       <c r="G94">
-        <v>-7.173450131347027</v>
+        <v>-9.647500265937328</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.535567413249382</v>
       </c>
       <c r="E95">
-        <v>-35.51830905834073</v>
+        <v>-35.29964263393235</v>
       </c>
       <c r="F95">
-        <v>-3.710992506272777</v>
+        <v>-4.961119030370637</v>
       </c>
       <c r="G95">
-        <v>-9.132571391668009</v>
+        <v>-9.404036125888245</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.791776547413951</v>
       </c>
       <c r="E96">
-        <v>-37.31939411880442</v>
+        <v>-37.49691709261611</v>
       </c>
       <c r="F96">
-        <v>-4.497920829747237</v>
+        <v>-4.727964256076479</v>
       </c>
       <c r="G96">
-        <v>-8.724645970319013</v>
+        <v>-11.44814240074786</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.039674668383297</v>
       </c>
       <c r="E97">
-        <v>-38.83489323021139</v>
+        <v>-38.44183527176762</v>
       </c>
       <c r="F97">
-        <v>-4.640815863464957</v>
+        <v>-4.99496198061201</v>
       </c>
       <c r="G97">
-        <v>-9.868234200313774</v>
+        <v>-10.75209358002501</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.261224034632292</v>
       </c>
       <c r="E98">
-        <v>-40.37210863872212</v>
+        <v>-41.46820539414571</v>
       </c>
       <c r="F98">
-        <v>-4.789778688408184</v>
+        <v>-5.176027355883329</v>
       </c>
       <c r="G98">
-        <v>-8.968355090738001</v>
+        <v>-11.0541974132112</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.448706887827473</v>
       </c>
       <c r="E99">
-        <v>-42.73904690457726</v>
+        <v>-43.93792869878993</v>
       </c>
       <c r="F99">
-        <v>-4.945511760134491</v>
+        <v>-5.237490560436247</v>
       </c>
       <c r="G99">
-        <v>-9.938040363554846</v>
+        <v>-12.06634374311474</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.59791307886187</v>
       </c>
       <c r="E100">
-        <v>-44.98227405325385</v>
+        <v>-45.63684912140358</v>
       </c>
       <c r="F100">
-        <v>-4.507625153871033</v>
+        <v>-5.132685516634053</v>
       </c>
       <c r="G100">
-        <v>-9.617854330633154</v>
+        <v>-11.51674683595818</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.691036279562905</v>
       </c>
       <c r="E101">
-        <v>-47.02440978514583</v>
+        <v>-46.55999892600021</v>
       </c>
       <c r="F101">
-        <v>-4.73526714309956</v>
+        <v>-5.290595537894918</v>
       </c>
       <c r="G101">
-        <v>-9.074550770546741</v>
+        <v>-12.2710447054445</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.722726890562955</v>
       </c>
       <c r="E102">
-        <v>-48.96405596117772</v>
+        <v>-49.30837282175843</v>
       </c>
       <c r="F102">
-        <v>-5.418880655729462</v>
+        <v>-5.034934849634101</v>
       </c>
       <c r="G102">
-        <v>-9.930886274644481</v>
+        <v>-11.93283606260701</v>
       </c>
     </row>
   </sheetData>
